--- a/artfynd/A 34439-2023 artfynd.xlsx
+++ b/artfynd/A 34439-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34439-2023 artfynd.xlsx
+++ b/artfynd/A 34439-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16634280</v>
+        <v>111869843</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strupenskogen, Ög</t>
+          <t>Betlehem SV 1090 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576535.6051506037</v>
+        <v>576563</v>
       </c>
       <c r="R2" t="n">
-        <v>6510523.012983799</v>
+        <v>6510574</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>C:a 20 plantor. En del plantor skadade av vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,30 +779,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16634281</v>
+        <v>111869946</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,39 +810,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strupenskogen, Ög</t>
+          <t>Betlehem SV 1100 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576535.6051506037</v>
+        <v>576559</v>
       </c>
       <c r="R3" t="n">
-        <v>6510523.012983799</v>
+        <v>6510607</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +880,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En del plantor skadade av vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,71 +903,80 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16634282</v>
+        <v>111870086</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strupenskogen, Ög</t>
+          <t>Betlehem SV 1260 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576535.6051506037</v>
+        <v>576558</v>
       </c>
       <c r="R4" t="n">
-        <v>6510523.012983799</v>
+        <v>6510419</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +1000,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,33 +1014,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16634268</v>
+        <v>111870176</v>
       </c>
       <c r="B5" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>97990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,47 +1049,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>224358</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strupenskogen, Ög</t>
+          <t>Betlehem SV 1255 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576535.6051506037</v>
+        <v>576523</v>
       </c>
       <c r="R5" t="n">
-        <v>6510523.012983799</v>
+        <v>6510439</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1111,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,30 +1129,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111869946</v>
+        <v>111870258</v>
       </c>
       <c r="B6" t="n">
-        <v>103755</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,50 +1160,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>224361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Betlehem SV 1100 m, Ög</t>
+          <t>Betlehem SV 1200 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576559</v>
+        <v>576472</v>
       </c>
       <c r="R6" t="n">
-        <v>6510607</v>
+        <v>6510557</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,11 +1226,6 @@
           <t>2023-09-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En del plantor skadade av vildsvinsbök.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1254,7 +1238,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Mossbevuxen bergklack i barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1269,479 +1253,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>111870086</v>
-      </c>
-      <c r="B7" t="n">
-        <v>103755</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Betlehem SV 1260 m, Ög</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>576558</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6510419</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Krokek</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>111869843</v>
-      </c>
-      <c r="B8" t="n">
-        <v>103755</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Betlehem SV 1090 m, Ög</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>576563</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6510574</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Krokek</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>C:a 20 plantor. En del plantor skadade av vildsvinsbök.</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>111870176</v>
-      </c>
-      <c r="B9" t="n">
-        <v>95694</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>224358</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vanlig plattlummer</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Betlehem SV 1255 m, Ög</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>576523</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6510439</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Krokek</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>111870258</v>
-      </c>
-      <c r="B10" t="n">
-        <v>95682</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>224361</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vanlig lopplummer</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Huperzia selago subsp. selago</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Betlehem SV 1200 m, Ög</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>576472</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6510557</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Krokek</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Mossbevuxen bergklack i barrskog</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34439-2023 artfynd.xlsx
+++ b/artfynd/A 34439-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111869843</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111869946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111870086</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111870176</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,8 +1278,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111870258</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>